--- a/downloads/Conference-Storyboard.xlsx
+++ b/downloads/Conference-Storyboard.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="1" r:id="R3173031c180d4c01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank template" sheetId="2" r:id="Rb61cb290024e4e67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed example" sheetId="3" r:id="R63ae8a8c876a4768"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="1" r:id="R6f5377e4795c46ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank template" sheetId="2" r:id="R8cdb8a1706c340ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed example" sheetId="3" r:id="R7613fa2425234d7a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -155,7 +155,7 @@
         <x:color rgb="FF8C3225"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE3DC"/>
         </x:patternFill>
       </x:fill>
@@ -165,7 +165,7 @@
         <x:color rgb="FF8C3225"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE3DC"/>
         </x:patternFill>
       </x:fill>
@@ -383,7 +383,7 @@
     </x:row>
     <x:row r="2" ht="47" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>Dental Research AI • Free, editable Excel worksheet • Version 2 • 8 September 2026</x:v>
+        <x:v>Dental Research AI • Free editable worksheet • Version 3 • 9 September 2026</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -420,7 +420,7 @@
         <x:v>1. Read the example</x:v>
       </x:c>
       <x:c r="B6" s="4" t="str">
-        <x:v>Open Completed example. Every study, event, source excerpt, tool record, and action in that sheet is invented for teaching.</x:v>
+        <x:v>Read the Completed example. Published facts are cited to JOP. Proposed plans, practice errors, imagined comments, and AI-use records are labeled teaching exercises; they are not the authors’ original records.</x:v>
       </x:c>
       <x:c r="C6" s="12" t="str">
         <x:v>Green = example</x:v>
@@ -481,12 +481,12 @@
         <x:v>Use approved storage</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="86" customHeight="1">
+    <x:row r="12" ht="150" customHeight="1">
       <x:c r="A12" s="11" t="str">
         <x:v>Sources / limits</x:v>
       </x:c>
       <x:c r="B12" s="4" t="str">
-        <x:v>Event rules are hypothetical in the example. For your talk, record the actual official event URL, date checked, format, disclosures, rights, and embargo requirements.</x:v>
+        <x:v>Xu B, Wang Y, Zhang L, Lin WS, Tan J, Chen L. Journal of Prosthodontics. 2026. Early View; supplied PDF pp. 1–7. Performance of a residual neural network system versus dental technicians for gingival porcelain shade matching https://onlinelibrary.wiley.com/doi/full/10.1111/jopr.70151 Methods, PDF pp. 2–4; Results and Tables 2–3, PDF pp. 4–6; Discussion, PDF p. 6.</x:v>
       </x:c>
       <x:c r="C12" s="4" t="str">
         <x:v>Recheck current guidance</x:v>
@@ -508,7 +508,7 @@
         <x:v>Calculation legend</x:v>
       </x:c>
       <x:c r="B14" s="4" t="str">
-        <x:v>Yellow cells are editable inputs; green cells on the example sheet contain invented entries. Dark teal total rows, if present, contain formulas. Do not replace formulas with typed totals.</x:v>
+        <x:v>Yellow cells are editable; green example cells contain published facts and clearly labeled teaching entries. Dark teal timing totals contain formulas. Preserve formulas when editing.</x:v>
       </x:c>
       <x:c r="C14" s="4" t="str">
         <x:v>No color-only status codes</x:v>
@@ -798,7 +798,7 @@
   <x:sheetData>
     <x:row r="1" ht="46" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>Example: an eight-minute research talk</x:v>
+        <x:v>Example: eight-minute presentation of Xu et al.</x:v>
       </x:c>
       <x:c r="B1" s="6"/>
       <x:c r="C1" s="6"/>
@@ -808,7 +808,7 @@
     </x:row>
     <x:row r="2" ht="47" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>COMPLETED EXAMPLE • Invented study and event timings. All numerical findings are stipulated teaching data.</x:v>
+        <x:v>Published study findings; slide wording and 8 + 2 minute format are teaching choices, not conference rules.</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -855,7 +855,7 @@
     </x:row>
     <x:row r="5" ht="62" customHeight="1">
       <x:c r="A5" s="12" t="str">
-        <x:v>Scenario requirement: 8-minute talk + separate 2-minute Q&amp;A. No patient or generated research images. Confirm actual event rules before real use.</x:v>
+        <x:v>Teaching format: 8 minutes speaking + separate 2 minutes Q&amp;A. Published-study presentation, with original source-cited visuals. Confirm actual event rules.</x:v>
       </x:c>
       <x:c r="B5" s="12"/>
       <x:c r="C5" s="12"/>
@@ -888,16 +888,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B7" s="12" t="str">
-        <x:v>Two scanners, the same casts</x:v>
+        <x:v>Can AI improve shade matching?</x:v>
       </x:c>
       <x:c r="C7" s="12" t="str">
-        <x:v>Question and disclosures</x:v>
+        <x:v>Question and attribution</x:v>
       </x:c>
       <x:c r="D7" s="12" t="str">
-        <x:v>Approved teaching abstract; no external funding/conflicts; AI assisted outline, authors checked it.</x:v>
+        <x:v>Exact study title, authors and DOI. Add the presenter’s actual AI-preparation disclosure.</x:v>
       </x:c>
       <x:c r="E7" s="12" t="str">
-        <x:v>Introduce a bounded laboratory comparison.</x:v>
+        <x:v>Present published work; do not claim a new study.</x:v>
       </x:c>
       <x:c r="F7" s="17" t="n">
         <x:v>0.5</x:v>
@@ -908,16 +908,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B8" s="12" t="str">
-        <x:v>Measure reference agreement</x:v>
+        <x:v>The comparison is paired</x:v>
       </x:c>
       <x:c r="C8" s="12" t="str">
-        <x:v>Define the outcome</x:v>
+        <x:v>Explain design</x:v>
       </x:c>
       <x:c r="D8" s="12" t="str">
-        <x:v>Definition: mean absolute surface deviation (µm).</x:v>
+        <x:v>18 volunteers, each with technician and ResNet specimens. Methods.</x:v>
       </x:c>
       <x:c r="E8" s="12" t="str">
-        <x:v>This measure is not a clinical outcome.</x:v>
+        <x:v>Both methods belong to the same person.</x:v>
       </x:c>
       <x:c r="F8" s="17" t="n">
         <x:v>1</x:v>
@@ -928,19 +928,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B9" s="12" t="str">
-        <x:v>Ten casts, paired devices</x:v>
+        <x:v>Three zones, one metric</x:v>
       </x:c>
       <x:c r="C9" s="12" t="str">
-        <x:v>Explain the design</x:v>
+        <x:v>Define observations</x:v>
       </x:c>
       <x:c r="D9" s="12" t="str">
-        <x:v>Workflow: 10 casts × A/B × 3 technical scans; average within cast/device.</x:v>
+        <x:v>Upper, middle, lower zones; dimensionless CIEDE2000 ΔE00. Methods.</x:v>
       </x:c>
       <x:c r="E9" s="12" t="str">
-        <x:v>The cast is the paired unit, not the scan.</x:v>
+        <x:v>Repeated measurements are not independent patients.</x:v>
       </x:c>
       <x:c r="F9" s="17" t="n">
-        <x:v>1.5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="106" customHeight="1">
@@ -948,19 +948,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B10" s="12" t="str">
-        <x:v>Lower mean deviation for B</x:v>
+        <x:v>Lower overall color difference</x:v>
       </x:c>
       <x:c r="C10" s="12" t="str">
-        <x:v>Present verified results</x:v>
+        <x:v>Present result</x:v>
       </x:c>
       <x:c r="D10" s="12" t="str">
-        <x:v>A 70 µm; B 62 µm; B−A -8 µm, supplied 95% CI -13 to -3 µm.</x:v>
+        <x:v>ResNet 4.169 ± 2.048; technicians 5.625 ± 1.967; p &lt; 0.001. Results/Table 2.</x:v>
       </x:c>
       <x:c r="E10" s="12" t="str">
-        <x:v>Use the verified summary table; do not invent individual values.</x:v>
+        <x:v>Label ± as SD; preserve comparison direction.</x:v>
       </x:c>
       <x:c r="F10" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>1.5</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="106" customHeight="1">
@@ -968,19 +968,19 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B11" s="12" t="str">
-        <x:v>What remains unknown</x:v>
+        <x:v>Zone findings differ</x:v>
       </x:c>
       <x:c r="C11" s="12" t="str">
-        <x:v>Explain limitations</x:v>
+        <x:v>Show regional result</x:v>
       </x:c>
       <x:c r="D11" s="12" t="str">
-        <x:v>One operator; manufactured casts; no clinical outcome or mechanism test.</x:v>
+        <x:v>Upper p = 0.317; middle p &lt; 0.001; lower p = 0.007. Results.</x:v>
       </x:c>
       <x:c r="E11" s="12" t="str">
-        <x:v>Discuss limits on generalizability.</x:v>
+        <x:v>Nonsignificance does not establish equivalence.</x:v>
       </x:c>
       <x:c r="F11" s="17" t="n">
-        <x:v>1.5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="106" customHeight="1">
@@ -988,36 +988,60 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B12" s="12" t="str">
-        <x:v>A bounded finding</x:v>
+        <x:v>Improved does not mean acceptable</x:v>
       </x:c>
       <x:c r="C12" s="12" t="str">
-        <x:v>State the conclusion</x:v>
+        <x:v>Explain threshold</x:v>
       </x:c>
       <x:c r="D12" s="12" t="str">
-        <x:v>Approved teaching abstract conclusion.</x:v>
+        <x:v>Acceptability threshold 2.8; both overall means exceed it. Methods/Results.</x:v>
       </x:c>
       <x:c r="E12" s="12" t="str">
-        <x:v>Lower mean deviation here does not establish clinical benefit.</x:v>
+        <x:v>Separate statistical and clinical interpretation.</x:v>
       </x:c>
       <x:c r="F12" s="17" t="n">
-        <x:v>1.5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="106" customHeight="1">
-      <x:c r="A13" s="12"/>
-      <x:c r="B13" s="12"/>
-      <x:c r="C13" s="12"/>
-      <x:c r="D13" s="12"/>
-      <x:c r="E13" s="12"/>
-      <x:c r="F13" s="17"/>
+      <x:c r="A13" s="12" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B13" s="12" t="str">
+        <x:v>Limits on generalization</x:v>
+      </x:c>
+      <x:c r="C13" s="12" t="str">
+        <x:v>Discuss scope</x:v>
+      </x:c>
+      <x:c r="D13" s="12" t="str">
+        <x:v>18 selected volunteers, two technicians, four powders; subjective evaluation n = 17.</x:v>
+      </x:c>
+      <x:c r="E13" s="12" t="str">
+        <x:v>Do not generalize to every gingival condition or system.</x:v>
+      </x:c>
+      <x:c r="F13" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="106" customHeight="1">
-      <x:c r="A14" s="12"/>
-      <x:c r="B14" s="12"/>
-      <x:c r="C14" s="12"/>
-      <x:c r="D14" s="12"/>
-      <x:c r="E14" s="12"/>
-      <x:c r="F14" s="17"/>
+      <x:c r="A14" s="12" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B14" s="12" t="str">
+        <x:v>A measured conclusion</x:v>
+      </x:c>
+      <x:c r="C14" s="12" t="str">
+        <x:v>Close and invite questions</x:v>
+      </x:c>
+      <x:c r="D14" s="12" t="str">
+        <x:v>Retain JOP citation and source-limited conclusion.</x:v>
+      </x:c>
+      <x:c r="E14" s="12" t="str">
+        <x:v>Better performance under tested conditions; further evaluation needed.</x:v>
+      </x:c>
+      <x:c r="F14" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="32" customHeight="1">
       <x:c r="A15" s="4"/>
@@ -1033,7 +1057,7 @@
       </x:c>
       <x:c r="B16" s="11"/>
       <x:c r="C16" s="12" t="str">
-        <x:v>One operator, manufactured casts, and no clinical outcomes. Calibration and interval-method details must be verified from the full study record.</x:v>
+        <x:v>Small selected sample; two technicians; four powders. Both overall means exceed the acceptability threshold. Objective n = 18; subjective n = 17.</x:v>
       </x:c>
       <x:c r="D16" s="12"/>
       <x:c r="E16" s="12"/>
@@ -1053,7 +1077,7 @@
       </x:c>
       <x:c r="B18" s="11"/>
       <x:c r="C18" s="12" t="str">
-        <x:v>Prepare verified notes on unit, measurement, missing data, calibration, and interval method. Say when a question is not answerable from the study.</x:v>
+        <x:v>Prepare answers about pairing, repeated zones, clinical thresholds, missing subjective data, and generalization. Keep the original JOP paper available.</x:v>
       </x:c>
       <x:c r="D18" s="12"/>
       <x:c r="E18" s="12"/>
@@ -1073,7 +1097,7 @@
       </x:c>
       <x:c r="B20" s="11"/>
       <x:c r="C20" s="12" t="str">
-        <x:v>Check numbers, fonts, contrast, permissions, disclosure, and author approval. Rehearsal has NOT YET BEEN DONE in this teaching record.</x:v>
+        <x:v>Recheck all slide facts, readability, permissions, presenter disclosures, and any required author approval. Actual rehearsal is NOT YET DONE in this teaching record.</x:v>
       </x:c>
       <x:c r="D20" s="12"/>
       <x:c r="E20" s="12"/>
